--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1244EF10-CF5C-4EC6-8776-FAD0FF470506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29ADED64-74F3-4406-BE9A-59D7EE7A2969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="-15615" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17130" yWindow="-15405" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -99,6 +99,23 @@
     <t>杖C</t>
     <rPh sb="0" eb="1">
       <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HPが{0}回復した</t>
+    <rPh sb="6" eb="8">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度が{0}回復した</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -460,7 +477,7 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
@@ -501,7 +518,9 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -510,7 +529,9 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29ADED64-74F3-4406-BE9A-59D7EE7A2969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7AAF73-AEBA-4BBB-BA2F-D961B80FA2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17130" yWindow="-15405" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9990" yWindow="-15615" windowWidth="18030" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7AAF73-AEBA-4BBB-BA2F-D961B80FA2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B07456-65BB-46A7-A518-C769AB55EA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9990" yWindow="-15615" windowWidth="18030" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="-15210" windowWidth="19680" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -86,16 +86,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>食べ物B</t>
-    <rPh sb="0" eb="1">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>モノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>杖C</t>
     <rPh sb="0" eb="1">
       <t>ツエ</t>
@@ -116,6 +106,43 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肉</t>
+    <rPh sb="0" eb="1">
+      <t>ニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼けた肉</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐った肉</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒焦げ肉</t>
+    <rPh sb="0" eb="2">
+      <t>クロコ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -473,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -519,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -530,7 +557,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -643,10 +670,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3">
-        <v>2001</v>
+        <v>2100</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -654,14 +681,47 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3">
-        <v>2002</v>
+        <v>2101</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2102</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2103</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B07456-65BB-46A7-A518-C769AB55EA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DE9A33-52DB-4F25-9756-5D0C638333E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="-15210" windowWidth="19680" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{0}ダメージ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -93,23 +89,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HPが{0}回復した</t>
-    <rPh sb="6" eb="8">
-      <t>カイフク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>満腹度が{0}回復した</t>
-    <rPh sb="0" eb="3">
-      <t>マンプクド</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カイフク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>肉</t>
     <rPh sb="0" eb="1">
       <t>ニク</t>
@@ -144,6 +123,79 @@
     <rPh sb="3" eb="4">
       <t>ニク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハエ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スライム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゾンビA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゾンビB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} に {1} ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} のHPが {1} 回復した</t>
+    <rPh sb="13" eb="15">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} の満腹度が {1} 回復した</t>
+    <rPh sb="5" eb="8">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐り攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} の {1}</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -500,11 +552,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
@@ -514,16 +566,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -531,13 +583,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -546,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -557,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -567,7 +619,9 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -640,7 +694,7 @@
         <v>1000</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -651,7 +705,7 @@
         <v>1001</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -662,7 +716,7 @@
         <v>2000</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -673,7 +727,7 @@
         <v>2100</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -684,7 +738,7 @@
         <v>2101</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -695,7 +749,7 @@
         <v>2102</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -706,7 +760,7 @@
         <v>2103</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -717,11 +771,152 @@
         <v>2200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
+        <v>10001</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>10002</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2">
+        <v>10003</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>10004</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2">
+        <v>10005</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>15001</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>15002</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>15003</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>15004</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3">
+        <v>15005</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3">
+        <v>15006</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DE9A33-52DB-4F25-9756-5D0C638333E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CB263C-2A53-48B0-B7F4-A08B154ED6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -196,6 +196,20 @@
   </si>
   <si>
     <t>{0} の {1}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} は焼けてしまった</t>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} は腐ってしまった</t>
+    <rPh sb="5" eb="6">
+      <t>クサ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -552,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -630,7 +644,9 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -639,7 +655,9 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -913,10 +931,23 @@
       <c r="A33" s="3">
         <v>15006</v>
       </c>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3">
+        <v>15007</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CB263C-2A53-48B0-B7F4-A08B154ED6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C978CD-E573-4D18-A12A-163AF1D49F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="-13125" windowWidth="15870" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -209,6 +209,13 @@
     <t>{0} は腐ってしまった</t>
     <rPh sb="5" eb="6">
       <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使う</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -566,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -949,6 +956,53 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>20000</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>20001</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>20002</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>20003</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>20004</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C978CD-E573-4D18-A12A-163AF1D49F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2435C542-05EA-4687-8C4C-17EF54A78AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="-13125" windowWidth="15870" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MessageData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -216,6 +216,27 @@
     <t>使う</t>
     <rPh sb="0" eb="1">
       <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>置く</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を置いた</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を置けなかった</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -673,7 +694,9 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -682,7 +705,9 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -971,7 +996,9 @@
       <c r="A36" s="2">
         <v>20001</v>
       </c>
-      <c r="B36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2435C542-05EA-4687-8C4C-17EF54A78AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03526C6C-30F5-4390-BDC2-4CBC8898B41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -237,6 +237,48 @@
     <t>{0} を置けなかった</t>
     <rPh sb="5" eb="6">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト武器</t>
+    <rPh sb="3" eb="5">
+      <t>ブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>てすと防具</t>
+    <rPh sb="3" eb="5">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装備</t>
+    <rPh sb="0" eb="2">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外す</t>
+    <rPh sb="0" eb="1">
+      <t>ハズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を装備した</t>
+    <rPh sb="5" eb="7">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0} を外した</t>
+    <rPh sb="5" eb="6">
+      <t>ハズ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -594,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -716,7 +758,9 @@
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -725,7 +769,9 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -740,44 +786,38 @@
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3">
-        <v>1000</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -785,10 +825,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3">
-        <v>2101</v>
+        <v>1001</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -796,10 +836,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3">
-        <v>2102</v>
+        <v>2000</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -807,10 +847,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -818,10 +858,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3">
-        <v>2200</v>
+        <v>2101</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -829,21 +869,21 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3">
-        <v>10000</v>
+        <v>2102</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2">
-        <v>10001</v>
+      <c r="A22" s="3">
+        <v>2103</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -851,21 +891,21 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3">
-        <v>10002</v>
+        <v>2200</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2">
-        <v>10003</v>
+      <c r="A24" s="3">
+        <v>2600</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -873,32 +913,32 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3">
-        <v>10004</v>
+        <v>2700</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2">
-        <v>10005</v>
+      <c r="A26" s="3">
+        <v>10000</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3">
-        <v>15000</v>
+      <c r="A27" s="2">
+        <v>10001</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -906,21 +946,21 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3">
-        <v>15001</v>
+        <v>10002</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3">
-        <v>15002</v>
+      <c r="A29" s="2">
+        <v>10003</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -928,21 +968,21 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3">
-        <v>15003</v>
+        <v>10004</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3">
-        <v>15004</v>
+      <c r="A31" s="2">
+        <v>10005</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -950,10 +990,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3">
-        <v>15005</v>
+        <v>15000</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -961,10 +1001,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3">
-        <v>15006</v>
+        <v>15001</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -972,63 +1012,122 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3">
-        <v>15007</v>
+        <v>15002</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>20000</v>
+      <c r="A35" s="3">
+        <v>15003</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>20001</v>
+      <c r="A36" s="3">
+        <v>15004</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>20002</v>
-      </c>
-      <c r="B37" s="2"/>
+      <c r="A37" s="3">
+        <v>15005</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>20003</v>
-      </c>
-      <c r="B38" s="2"/>
+      <c r="A38" s="3">
+        <v>15006</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>20004</v>
-      </c>
-      <c r="B39" s="2"/>
+      <c r="A39" s="3">
+        <v>15007</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>20000</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>20001</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>20002</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>20003</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>20004</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
